--- a/instrumentos/sesion-06/Sesion 6.xlsx
+++ b/instrumentos/sesion-06/Sesion 6.xlsx
@@ -1913,6 +1913,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -2023,7 +2024,7 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>46322.375</v>
+        <v>46314.375</v>
       </c>
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="19" t="n"/>
@@ -2035,7 +2036,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>46328.99930555555</v>
+        <v>46320.99930555555</v>
       </c>
       <c r="D13" s="18" t="n"/>
       <c r="E13" s="19" t="n"/>
@@ -2054,6 +2055,7 @@
       <c r="D14" s="65" t="n"/>
       <c r="E14" s="66" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
@@ -4695,6 +4697,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="45" customHeight="1" s="62">
       <c r="A5" s="36" t="inlineStr">
         <is>
@@ -4804,10 +4807,10 @@
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>46328</v>
+        <v>46320</v>
       </c>
       <c r="E6" s="31" t="n">
         <v>168</v>
@@ -6607,7 +6610,7 @@
         <v/>
       </c>
       <c r="B5" s="39" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="C5" s="68" t="n">
         <v>0.7986111111111112</v>
@@ -6667,10 +6670,10 @@
         </is>
       </c>
       <c r="O5" s="39" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="P5" s="39" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
@@ -6693,7 +6696,7 @@
         <v/>
       </c>
       <c r="B6" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="C6" s="68" t="n">
         <v>0.4270833333333333</v>
@@ -6753,10 +6756,10 @@
         </is>
       </c>
       <c r="O6" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="P6" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
@@ -6779,7 +6782,7 @@
         <v/>
       </c>
       <c r="B7" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="C7" s="68" t="n">
         <v>0.4305555555555556</v>
@@ -6839,10 +6842,10 @@
         </is>
       </c>
       <c r="O7" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="P7" s="39" t="n">
-        <v>46322</v>
+        <v>46314</v>
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
@@ -6865,7 +6868,7 @@
         <v/>
       </c>
       <c r="B8" s="39" t="n">
-        <v>46323</v>
+        <v>46315</v>
       </c>
       <c r="C8" s="68" t="n">
         <v>0.6701388888888888</v>
@@ -6925,10 +6928,10 @@
         </is>
       </c>
       <c r="O8" s="39" t="n">
-        <v>46323</v>
+        <v>46315</v>
       </c>
       <c r="P8" s="39" t="n">
-        <v>46323</v>
+        <v>46315</v>
       </c>
       <c r="Q8" s="31" t="inlineStr">
         <is>
@@ -6951,7 +6954,7 @@
         <v/>
       </c>
       <c r="B9" s="39" t="n">
-        <v>46324</v>
+        <v>46316</v>
       </c>
       <c r="C9" s="68" t="n">
         <v>0.5</v>
@@ -7011,10 +7014,10 @@
         </is>
       </c>
       <c r="O9" s="39" t="n">
-        <v>46324</v>
+        <v>46316</v>
       </c>
       <c r="P9" s="39" t="n">
-        <v>46324</v>
+        <v>46316</v>
       </c>
       <c r="Q9" s="31" t="inlineStr">
         <is>
@@ -7037,7 +7040,7 @@
         <v/>
       </c>
       <c r="B10" s="39" t="n">
-        <v>46325</v>
+        <v>46317</v>
       </c>
       <c r="C10" s="68" t="n">
         <v>0.4597222222222222</v>
@@ -7097,10 +7100,10 @@
         </is>
       </c>
       <c r="O10" s="39" t="n">
-        <v>46325</v>
+        <v>46317</v>
       </c>
       <c r="P10" s="39" t="n">
-        <v>46325</v>
+        <v>46317</v>
       </c>
       <c r="Q10" s="31" t="inlineStr">
         <is>
@@ -7123,7 +7126,7 @@
         <v/>
       </c>
       <c r="B11" s="39" t="n">
-        <v>46327</v>
+        <v>46319</v>
       </c>
       <c r="C11" s="68" t="n">
         <v>0.4097222222222222</v>
@@ -7183,10 +7186,10 @@
         </is>
       </c>
       <c r="O11" s="39" t="n">
-        <v>46327</v>
+        <v>46319</v>
       </c>
       <c r="P11" s="39" t="n">
-        <v>46327</v>
+        <v>46319</v>
       </c>
       <c r="Q11" s="31" t="inlineStr">
         <is>
@@ -8950,6 +8953,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -9003,7 +9007,7 @@
       </c>
       <c r="E5" s="30" t="inlineStr">
         <is>
-          <t>Cronograma de campo y FM-01 (27/10 al 02/11, una semana)</t>
+          <t>Cronograma de campo y FM-01 (19/10 al 25/10, una semana)</t>
         </is>
       </c>
       <c r="F5" s="30" t="n"/>
@@ -9250,6 +9254,7 @@
       </c>
       <c r="F14" s="30" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -10429,6 +10434,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="39.75" customHeight="1" s="62">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -10958,6 +10964,7 @@
       <c r="J16" s="30" t="n"/>
       <c r="K16" s="30" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -12031,6 +12038,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="45" customHeight="1" s="62">
       <c r="A5" s="36" t="inlineStr">
         <is>
@@ -12089,7 +12097,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Duración de la intervención (27/10 al 02/11/2026)</t>
+          <t>Duración de la intervención (19/10 al 25/10/2026)</t>
         </is>
       </c>
       <c r="C6" s="31" t="n">
@@ -12245,7 +12253,7 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>Ventana de aplicación del postest (03/11 al 08/11/2026)</t>
+          <t>Ventana de aplicación del postest (03/11 al 31/10/2026)</t>
         </is>
       </c>
       <c r="C10" s="31" t="n">
@@ -12379,6 +12387,7 @@
       <c r="I15" s="30" t="n"/>
       <c r="J15" s="30" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -12401,6 +12410,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -13458,6 +13468,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="39.75" customHeight="1" s="62">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -13522,7 +13533,7 @@
         </is>
       </c>
       <c r="B5" s="39" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
@@ -13536,7 +13547,7 @@
       </c>
       <c r="E5" s="30" t="inlineStr">
         <is>
-          <t>7 días (27/10/2026 al 02/11/2026), al menos 3 sesiones</t>
+          <t>7 días (19/10/2026 al 25/10/2026), al menos 3 sesiones</t>
         </is>
       </c>
       <c r="F5" s="30" t="inlineStr">
@@ -13744,6 +13755,7 @@
       <c r="J19" s="30" t="n"/>
       <c r="K19" s="30" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="15.75" customHeight="1" s="62">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -14785,6 +14797,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -15002,6 +15015,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
@@ -16044,6 +16058,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
